--- a/data/trans_orig/P64S_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64S_2023_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las combinaciones de formas de desplazamiento que utilizan desde su casa al centro de trabajo/estudios en 2023</t>
+          <t>Población según las combinaciones de formas de desplazamiento que utilizan desde su casa al centro de trabajo/estudios en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44654</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>69840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211946</t>
+          <t>214853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247844</t>
+          <t>248063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130648</t>
+          <t>129195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157607</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354657</t>
+          <t>353435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400017</t>
+          <t>397248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36274</t>
+          <t>35182</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>61518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61928</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85403</t>
+          <t>85235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102884</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>138750</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>833</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37865</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58903</t>
+          <t>57853</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>37875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100674</t>
+          <t>99323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37585</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>42146</t>
+          <t>40855</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>31856</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>539343</t>
+          <t>534714</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>731768</t>
+          <t>729424</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>185970</t>
+          <t>187037</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>219454</t>
+          <t>220108</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>720001</t>
+          <t>721164</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1003794</t>
+          <t>996667</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>40468</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>138052</t>
+          <t>138226</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94294</t>
+          <t>92435</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>126339</t>
+          <t>125410</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>111461</t>
+          <t>107576</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>259358</t>
+          <t>260787</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>26973</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>38673</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>31882</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>939</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5936,12 +5936,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6049,12 +6049,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>247867</t>
+          <t>249077</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>285574</t>
+          <t>286593</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>194319</t>
+          <t>193702</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>245886</t>
+          <t>248130</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>456925</t>
+          <t>457217</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>516694</t>
+          <t>515747</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>347</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>441</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6212,47 +6212,47 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>3566</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>8261</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>1459</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>8495</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6275,12 +6275,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>31565</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>61429</t>
+          <t>60855</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>33746</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>63056</t>
+          <t>61731</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>71500</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>112945</t>
+          <t>113110</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>40873</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>69454</t>
+          <t>69244</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>42890</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>46998</t>
+          <t>46809</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>78815</t>
+          <t>79751</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>839</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>918</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>23906</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>829</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>893</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
     </row>
@@ -7635,12 +7635,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>77272</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -7861,12 +7861,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>46006</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7876,82 +7876,82 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>40484</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>24577</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>55498</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>72939</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>55230</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>92881</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
           <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>40484</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>24433</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>53450</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>72939</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr">
-        <is>
-          <t>54007</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="inlineStr">
-        <is>
-          <t>91370</t>
-        </is>
-      </c>
-      <c r="U67" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>237078</t>
+          <t>234249</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>279705</t>
+          <t>280234</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>99850</t>
+          <t>95420</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>195302</t>
+          <t>196230</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>303269</t>
+          <t>322081</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>464490</t>
+          <t>467558</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8087,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>218373</t>
+          <t>241713</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8137,12 +8137,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>320351</t>
+          <t>282446</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -8200,12 +8200,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>76457</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>64788</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>126702</t>
+          <t>128585</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>127955</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>193032</t>
+          <t>191843</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>959</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>839</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8656,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>64720</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>122205</t>
+          <t>120127</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>94451</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>134040</t>
+          <t>134275</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>166426</t>
+          <t>165956</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>242918</t>
+          <t>244327</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>26775</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>58438</t>
+          <t>58507</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>67718</t>
+          <t>67387</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>68954</t>
+          <t>69560</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>116638</t>
+          <t>117304</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -8995,12 +8995,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -9334,12 +9334,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>52397</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>47722</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>52270</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>91520</t>
+          <t>91355</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9462,49 +9462,49 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>4649</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>12383</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="P81" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>4649</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>12040</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -9517,12 +9517,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>46044</t>
+          <t>46745</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>95817</t>
+          <t>95671</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>64768</t>
+          <t>65870</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>93939</t>
+          <t>93526</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>149025</t>
+          <t>149728</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>24280</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9786,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>63941</t>
+          <t>63550</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>48859</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>81956</t>
+          <t>81174</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>85866</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>133827</t>
+          <t>136866</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1290821</t>
+          <t>1289471</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1570176</t>
+          <t>1582215</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>616296</t>
+          <t>613242</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>784622</t>
+          <t>781422</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>1960398</t>
+          <t>1957840</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>2398168</t>
+          <t>2372491</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -10012,12 +10012,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>302738</t>
+          <t>298378</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>380438</t>
+          <t>369812</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -10125,12 +10125,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>156778</t>
+          <t>169556</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>288967</t>
+          <t>287713</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>281170</t>
+          <t>282811</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>371599</t>
+          <t>367794</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>429658</t>
+          <t>441969</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>639856</t>
+          <t>642717</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64S_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64S_2023_R-Habitat-trans_orig.xlsx
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>33699</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44079</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23004</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16621</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56223</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>46694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69840</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1064,22 +1064,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,22 +1699,22 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2116,67 +2116,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4656</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2194,32 +2194,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>232289</t>
+          <t>250947</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214853</t>
+          <t>231963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>248063</t>
+          <t>270246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2229,32 +2229,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>143622</t>
+          <t>156150</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129195</t>
+          <t>140971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155845</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>375910</t>
+          <t>407097</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353435</t>
+          <t>385599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>397248</t>
+          <t>432396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>12591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2420,32 +2420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47066</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35182</t>
+          <t>42601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61518</t>
+          <t>73803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2455,32 +2455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72656</t>
+          <t>75173</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60567</t>
+          <t>63731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85235</t>
+          <t>89415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2490,32 +2490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>119723</t>
+          <t>131273</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101047</t>
+          <t>112480</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138750</t>
+          <t>151649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>591139</t>
+          <t>645856</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>591139</t>
+          <t>645856</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>591139</t>
+          <t>645856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>48690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46940</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36976</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57853</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>73979</t>
+          <t>85961</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>70827</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99323</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>23024</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>35251</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -3554,32 +3554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3624,32 +3624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3667,32 +3667,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3815,32 +3815,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>28184</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40855</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3893,32 +3893,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3963,32 +3963,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4041,32 +4041,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4076,32 +4076,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4119,32 +4119,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>626375</t>
+          <t>412242</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>534714</t>
+          <t>384949</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>729424</t>
+          <t>438828</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>203646</t>
+          <t>220166</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>187037</t>
+          <t>198618</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>220108</t>
+          <t>237146</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4189,32 +4189,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>830020</t>
+          <t>632408</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>721164</t>
+          <t>599722</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>996667</t>
+          <t>664487</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -4232,32 +4232,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4277,12 +4277,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4302,32 +4302,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>89273</t>
+          <t>105122</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>83726</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>138226</t>
+          <t>126489</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4380,32 +4380,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>108460</t>
+          <t>122372</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>92435</t>
+          <t>103856</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125410</t>
+          <t>140522</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>197732</t>
+          <t>227493</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>107576</t>
+          <t>198013</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>260787</t>
+          <t>258055</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>805484</t>
+          <t>628041</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>805484</t>
+          <t>628041</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>805484</t>
+          <t>628041</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>400881</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>400881</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>400881</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1206364</t>
+          <t>1075103</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1206364</t>
+          <t>1075103</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1206364</t>
+          <t>1075103</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>34070</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>45491</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5479,32 +5479,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>24745</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5514,32 +5514,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5549,32 +5549,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -5627,32 +5627,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5662,32 +5662,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5705,67 +5705,67 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>8867</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>15623</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>7994</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5775,32 +5775,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>748</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5888,27 +5888,27 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -5931,32 +5931,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5966,32 +5966,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6001,32 +6001,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -6044,32 +6044,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>269437</t>
+          <t>309362</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>249077</t>
+          <t>286590</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>286593</t>
+          <t>329100</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>214771</t>
+          <t>204751</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>193702</t>
+          <t>188635</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>248130</t>
+          <t>221715</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6114,32 +6114,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>484207</t>
+          <t>514112</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>457217</t>
+          <t>487585</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>515747</t>
+          <t>537807</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -6157,32 +6157,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6192,32 +6192,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6227,32 +6227,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -6270,32 +6270,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>43483</t>
+          <t>46027</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>60855</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6305,32 +6305,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>48094</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>61731</t>
+          <t>72838</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>92194</t>
+          <t>106297</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>88293</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>113110</t>
+          <t>126371</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>417570</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>417570</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>417570</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>322393</t>
+          <t>337565</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>322393</t>
+          <t>337565</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>322393</t>
+          <t>337565</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>755135</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>755135</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>755135</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6726,32 +6726,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>40150</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>37142</t>
+          <t>37122</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>54104</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>40873</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>69244</t>
+          <t>66587</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6839,32 +6839,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>50799</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6874,32 +6874,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>46809</t>
+          <t>43743</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6909,32 +6909,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>58096</t>
+          <t>67120</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>53429</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>79751</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>912</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>912</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7404,32 +7404,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7474,32 +7474,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>23107</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -7630,32 +7630,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7665,32 +7665,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7700,32 +7700,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>41874</t>
+          <t>53761</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>77272</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -7743,32 +7743,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7778,32 +7778,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7813,32 +7813,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -7856,32 +7856,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>40683</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>57481</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7891,32 +7891,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>46784</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>55498</t>
+          <t>60173</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>72939</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>55230</t>
+          <t>70741</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>92881</t>
+          <t>106888</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -7969,32 +7969,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>259184</t>
+          <t>273140</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>234249</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>280234</t>
+          <t>297273</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8004,32 +8004,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>162189</t>
+          <t>169258</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>151657</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>196230</t>
+          <t>186702</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8039,32 +8039,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>421373</t>
+          <t>442398</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>322081</t>
+          <t>414251</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>467558</t>
+          <t>472274</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -8082,32 +8082,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8117,32 +8117,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>75564</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>241713</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8152,32 +8152,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>86654</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>282446</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -8195,32 +8195,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>85743</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8230,32 +8230,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>104038</t>
+          <t>113428</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>98544</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>128585</t>
+          <t>129526</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8265,32 +8265,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>164608</t>
+          <t>181281</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>129111</t>
+          <t>160358</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>191843</t>
+          <t>205234</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>516717</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>516717</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>516717</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8343,17 +8343,17 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8378,17 +8378,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>950688</t>
+          <t>964379</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>950688</t>
+          <t>964379</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>950688</t>
+          <t>964379</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -8651,32 +8651,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>97671</t>
+          <t>107756</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>130195</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>114299</t>
+          <t>125338</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>94451</t>
+          <t>109454</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>134275</t>
+          <t>143610</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8721,32 +8721,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>211970</t>
+          <t>233094</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>165956</t>
+          <t>207429</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>244327</t>
+          <t>264447</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -8764,32 +8764,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>53654</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>39921</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>70517</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8799,32 +8799,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>43192</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>67387</t>
+          <t>70042</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8834,32 +8834,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>91230</t>
+          <t>110268</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>69560</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>117304</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -9103,32 +9103,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9173,32 +9173,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -9329,32 +9329,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>29229</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>50689</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9364,32 +9364,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9399,32 +9399,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>71392</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>63283</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>91355</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -9442,32 +9442,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9477,22 +9477,22 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9512,32 +9512,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -9555,32 +9555,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>65642</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>95671</t>
+          <t>106185</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9590,32 +9590,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>50729</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t>47487</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>65870</t>
+          <t>75552</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9625,32 +9625,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>122179</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>93526</t>
+          <t>123646</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>174738</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -9668,32 +9668,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9703,32 +9703,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9738,32 +9738,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -9781,32 +9781,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>63550</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9816,32 +9816,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>63967</t>
+          <t>76627</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>61558</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>92663</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9851,32 +9851,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>110861</t>
+          <t>136805</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>85866</t>
+          <t>113176</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>161836</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9894,32 +9894,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>1387284</t>
+          <t>1245691</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1289471</t>
+          <t>1200853</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1582215</t>
+          <t>1290981</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>724227</t>
+          <t>750324</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>613242</t>
+          <t>710437</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>781422</t>
+          <t>786010</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9964,32 +9964,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>2111512</t>
+          <t>1996016</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>1957840</t>
+          <t>1935581</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>2372491</t>
+          <t>2050118</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -10007,32 +10007,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>47174</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>77693</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>298378</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10077,32 +10077,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>94950</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>369812</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10120,32 +10120,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>240393</t>
+          <t>275103</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>169556</t>
+          <t>242433</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>287713</t>
+          <t>311849</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>333866</t>
+          <t>371242</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>282811</t>
+          <t>342012</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>367794</t>
+          <t>399615</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10190,32 +10190,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>574258</t>
+          <t>646345</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>441969</t>
+          <t>598013</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>642717</t>
+          <t>691441</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -10233,17 +10233,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10303,17 +10303,17 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
